--- a/Fase 3/Evidencias Grupales/PLANILLA DE EVALUACIÓN FASE 3 - PRESENTACION FINAL.xlsx
+++ b/Fase 3/Evidencias Grupales/PLANILLA DE EVALUACIÓN FASE 3 - PRESENTACION FINAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29523"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://duoccl0-my.sharepoint.com/personal/ge_galan_profesor_duoc_cl/Documents/2024-2/Clases/CAPSTONE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PARA CORREGIR (2-2025)\CAPSTONE\SEC 2\grupo 2 (Castillo - Cardenas  - Vargas)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="778" documentId="8_{2EFDF332-31E9-4C74-A6B5-E695634C1C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03EBA376-E4C1-4AD7-96DD-CB6E03189E9F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B22440D-85B3-487E-9FD5-4A88A1CD1FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVALUACION FASE 3" sheetId="1" r:id="rId1"/>
@@ -57,9 +57,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -78,15 +79,6 @@
   </si>
   <si>
     <t>Nota final</t>
-  </si>
-  <si>
-    <t>Axel Cardenas</t>
-  </si>
-  <si>
-    <t>Diego Castillo</t>
-  </si>
-  <si>
-    <t>Diego Vargas</t>
   </si>
   <si>
     <t>DOCENTE</t>
@@ -289,6 +281,15 @@
   </si>
   <si>
     <t>Muy Relevante</t>
+  </si>
+  <si>
+    <t>Axel Cardenas</t>
+  </si>
+  <si>
+    <t>Diego Castillo</t>
+  </si>
+  <si>
+    <t>Diego Vargas</t>
   </si>
 </sst>
 </file>
@@ -830,15 +831,23 @@
     <xf numFmtId="164" fontId="0" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -869,15 +878,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -913,7 +914,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1210,7 +1211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:K797"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="66.85546875" customWidth="1"/>
@@ -1224,7 +1225,7 @@
     <col min="12" max="24" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="14.45">
+    <row r="2" spans="1:11">
       <c r="C2" s="29">
         <v>0.7</v>
       </c>
@@ -1235,7 +1236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="14.45">
+    <row r="3" spans="1:11" ht="30">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1249,12 +1250,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="14.45">
+    <row r="4" spans="1:11">
       <c r="A4" s="3">
         <v>1</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="C4" s="31">
         <f>C21</f>
@@ -1269,12 +1270,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="14.45">
+    <row r="5" spans="1:11">
       <c r="A5" s="3">
         <v>2</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="C5" s="31">
         <f>C34</f>
@@ -1289,12 +1290,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="14.45">
+    <row r="6" spans="1:11">
       <c r="A6" s="3">
         <v>3</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="C6" s="31">
         <f>C47</f>
@@ -1309,59 +1310,59 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18" outlineLevel="1">
-      <c r="A11" s="42" t="s">
-        <v>7</v>
+    <row r="11" spans="1:11" ht="18.75" outlineLevel="1">
+      <c r="A11" s="48" t="s">
+        <v>4</v>
       </c>
       <c r="B11" s="11" t="str">
         <f>B4</f>
         <v>Axel Cardenas</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="46"/>
+    </row>
+    <row r="12" spans="1:11" outlineLevel="1">
+      <c r="A12" s="40"/>
+      <c r="B12" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="42"/>
+      <c r="D12" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="E12" s="46"/>
+      <c r="F12" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="52"/>
-    </row>
-    <row r="12" spans="1:11" ht="14.45" outlineLevel="1">
-      <c r="A12" s="53"/>
-      <c r="B12" s="15" t="s">
+      <c r="G12" s="46"/>
+      <c r="H12" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="40" t="s">
+      <c r="I12" s="46"/>
+      <c r="J12" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="52"/>
-      <c r="F12" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="52"/>
-      <c r="H12" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="52"/>
-      <c r="J12" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="52"/>
+      <c r="K12" s="46"/>
     </row>
     <row r="13" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A13" s="55"/>
+      <c r="A13" s="41"/>
       <c r="B13" s="19" t="str">
         <f>RUBRICA!A4</f>
         <v xml:space="preserve">1. Presenta el proyecto considerando la relevancia, objetivos, metodología y desarrollo, de acuerdo a los estándares de calidad de la disciplina. </v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D13" s="12" t="str">
         <f t="shared" ref="D13:D17" si="1">IF($C13=CL,"X","")</f>
@@ -1397,13 +1398,13 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="26.45" customHeight="1" outlineLevel="1">
-      <c r="A14" s="55"/>
+      <c r="A14" s="41"/>
       <c r="B14" s="19" t="str">
         <f>RUBRICA!A5</f>
         <v xml:space="preserve">2. Presenta las evidencias del Proyecto APT, dando cuenta del cumplimiento de los objetivos y de acuerdo a los estándares de la disciplina. </v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D14" s="12" t="str">
         <f t="shared" si="1"/>
@@ -1439,13 +1440,13 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A15" s="55"/>
+      <c r="A15" s="41"/>
       <c r="B15" s="19" t="str">
         <f>RUBRICA!A6</f>
         <v>3. Responde las preguntas realizadas por la comisión, cumpliendo con los estándares de calidad de la disciplina.</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D15" s="12" t="str">
         <f t="shared" si="1"/>
@@ -1481,13 +1482,13 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A16" s="55"/>
+      <c r="A16" s="41"/>
       <c r="B16" s="19" t="str">
         <f>RUBRICA!A7</f>
         <v>4. Expone el Proyecto APT, considerando el formato y el tiempo establecido para la presentación.</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D16" s="12" t="str">
         <f t="shared" si="1"/>
@@ -1523,13 +1524,13 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A17" s="55"/>
+      <c r="A17" s="41"/>
       <c r="B17" s="19" t="str">
         <f>RUBRICA!A8</f>
         <v>5. Expresa sus ideas con fluidez, claridad y precisión, utilizando lenguaje técnico propio de la disciplina.</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D17" s="12" t="str">
         <f t="shared" si="1"/>
@@ -1564,14 +1565,14 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A18" s="55"/>
+    <row r="18" spans="1:11" ht="36" outlineLevel="1">
+      <c r="A18" s="41"/>
       <c r="B18" s="19" t="str">
         <f>RUBRICA!A9</f>
         <v>6. Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estructura y nombres solicitados, guardando todas las evidencias de avances en Git</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D18" s="12" t="str">
         <f>IF($C18=CL,"X","")</f>
@@ -1607,13 +1608,13 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A19" s="55"/>
+      <c r="A19" s="41"/>
       <c r="B19" s="19" t="str">
         <f>RUBRICA!A10</f>
         <v xml:space="preserve">7. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. </v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D19" s="12" t="str">
         <f>IF($C19=CL,"X","")</f>
@@ -1649,9 +1650,9 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1" outlineLevel="1">
-      <c r="A20" s="53"/>
+      <c r="A20" s="40"/>
       <c r="B20" s="18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C20" s="22">
         <f>E20+G20+I20+K20</f>
@@ -1679,9 +1680,9 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" outlineLevel="1">
-      <c r="A21" s="54"/>
+      <c r="A21" s="42"/>
       <c r="B21" s="21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C21" s="14">
         <f>VLOOKUP(C20,ESCALA_IEP!A2:B202,2,FALSE)</f>
@@ -1691,58 +1692,58 @@
     <row r="22" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="23" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="24" spans="1:11" ht="24" customHeight="1">
-      <c r="A24" s="42" t="s">
-        <v>7</v>
+      <c r="A24" s="48" t="s">
+        <v>4</v>
       </c>
       <c r="B24" s="11" t="str">
         <f>B5</f>
         <v>Diego Castillo</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="46"/>
+    </row>
+    <row r="25" spans="1:11" ht="24" customHeight="1">
+      <c r="A25" s="40"/>
+      <c r="B25" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="42"/>
+      <c r="D25" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="40" t="s">
+      <c r="E25" s="46"/>
+      <c r="F25" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="52"/>
-    </row>
-    <row r="25" spans="1:11" ht="24" customHeight="1">
-      <c r="A25" s="53"/>
-      <c r="B25" s="15" t="s">
+      <c r="G25" s="46"/>
+      <c r="H25" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="54"/>
-      <c r="D25" s="40" t="s">
+      <c r="I25" s="46"/>
+      <c r="J25" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="52"/>
-      <c r="F25" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="52"/>
-      <c r="H25" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="52"/>
-      <c r="J25" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" s="52"/>
+      <c r="K25" s="46"/>
     </row>
     <row r="26" spans="1:11" ht="24" customHeight="1">
-      <c r="A26" s="55"/>
+      <c r="A26" s="41"/>
       <c r="B26" s="19" t="str">
         <f>RUBRICA!A4</f>
         <v xml:space="preserve">1. Presenta el proyecto considerando la relevancia, objetivos, metodología y desarrollo, de acuerdo a los estándares de calidad de la disciplina. </v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D26" s="12" t="str">
         <f t="shared" ref="D26:D30" si="7">IF($C26=CL,"X","")</f>
@@ -1778,13 +1779,13 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="24" customHeight="1">
-      <c r="A27" s="55"/>
+      <c r="A27" s="41"/>
       <c r="B27" s="19" t="str">
         <f>RUBRICA!A5</f>
         <v xml:space="preserve">2. Presenta las evidencias del Proyecto APT, dando cuenta del cumplimiento de los objetivos y de acuerdo a los estándares de la disciplina. </v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D27" s="12" t="str">
         <f t="shared" si="7"/>
@@ -1820,13 +1821,13 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="24" customHeight="1">
-      <c r="A28" s="55"/>
+      <c r="A28" s="41"/>
       <c r="B28" s="19" t="str">
         <f>RUBRICA!A6</f>
         <v>3. Responde las preguntas realizadas por la comisión, cumpliendo con los estándares de calidad de la disciplina.</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D28" s="12" t="str">
         <f t="shared" si="7"/>
@@ -1862,13 +1863,13 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="24" customHeight="1">
-      <c r="A29" s="55"/>
+      <c r="A29" s="41"/>
       <c r="B29" s="19" t="str">
         <f>RUBRICA!A7</f>
         <v>4. Expone el Proyecto APT, considerando el formato y el tiempo establecido para la presentación.</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D29" s="12" t="str">
         <f t="shared" si="7"/>
@@ -1904,13 +1905,13 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="24" customHeight="1">
-      <c r="A30" s="55"/>
+      <c r="A30" s="41"/>
       <c r="B30" s="19" t="str">
         <f>RUBRICA!A8</f>
         <v>5. Expresa sus ideas con fluidez, claridad y precisión, utilizando lenguaje técnico propio de la disciplina.</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D30" s="12" t="str">
         <f t="shared" si="7"/>
@@ -1946,13 +1947,13 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="24" customHeight="1">
-      <c r="A31" s="55"/>
+      <c r="A31" s="41"/>
       <c r="B31" s="19" t="str">
         <f>RUBRICA!A9</f>
         <v>6. Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estructura y nombres solicitados, guardando todas las evidencias de avances en Git</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D31" s="12" t="str">
         <f>IF($C31=CL,"X","")</f>
@@ -1988,13 +1989,13 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="24" customHeight="1">
-      <c r="A32" s="55"/>
+      <c r="A32" s="41"/>
       <c r="B32" s="19" t="str">
         <f>RUBRICA!A10</f>
         <v xml:space="preserve">7. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. </v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D32" s="12" t="str">
         <f>IF($C32=CL,"X","")</f>
@@ -2030,9 +2031,9 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="24" customHeight="1">
-      <c r="A33" s="53"/>
+      <c r="A33" s="40"/>
       <c r="B33" s="18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C33" s="22">
         <f>E33+G33+I33+K33</f>
@@ -2060,9 +2061,9 @@
       </c>
     </row>
     <row r="34" spans="1:11" ht="24" customHeight="1">
-      <c r="A34" s="54"/>
+      <c r="A34" s="42"/>
       <c r="B34" s="21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C34" s="14">
         <f>VLOOKUP(C33,ESCALA_IEP!A15:B215,2,FALSE)</f>
@@ -2072,58 +2073,58 @@
     <row r="35" spans="1:11" ht="16.149999999999999" customHeight="1"/>
     <row r="36" spans="1:11" ht="13.9" customHeight="1"/>
     <row r="37" spans="1:11" ht="24" customHeight="1">
-      <c r="A37" s="42" t="s">
-        <v>7</v>
+      <c r="A37" s="48" t="s">
+        <v>4</v>
       </c>
       <c r="B37" s="11" t="str">
         <f>B6</f>
         <v>Diego Vargas</v>
       </c>
-      <c r="C37" s="39" t="s">
+      <c r="C37" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="46"/>
+    </row>
+    <row r="38" spans="1:11" ht="24" customHeight="1">
+      <c r="A38" s="40"/>
+      <c r="B38" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="42"/>
+      <c r="D38" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="40" t="s">
+      <c r="E38" s="46"/>
+      <c r="F38" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="52"/>
-    </row>
-    <row r="38" spans="1:11" ht="24" customHeight="1">
-      <c r="A38" s="53"/>
-      <c r="B38" s="15" t="s">
+      <c r="G38" s="46"/>
+      <c r="H38" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C38" s="54"/>
-      <c r="D38" s="40" t="s">
+      <c r="I38" s="46"/>
+      <c r="J38" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="52"/>
-      <c r="F38" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38" s="52"/>
-      <c r="H38" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="52"/>
-      <c r="J38" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="K38" s="52"/>
+      <c r="K38" s="46"/>
     </row>
     <row r="39" spans="1:11" ht="24" customHeight="1">
-      <c r="A39" s="55"/>
+      <c r="A39" s="41"/>
       <c r="B39" s="19" t="str">
         <f>RUBRICA!A4</f>
         <v xml:space="preserve">1. Presenta el proyecto considerando la relevancia, objetivos, metodología y desarrollo, de acuerdo a los estándares de calidad de la disciplina. </v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D39" s="12" t="str">
         <f t="shared" ref="D39:D43" si="12">IF($C39=CL,"X","")</f>
@@ -2159,13 +2160,13 @@
       </c>
     </row>
     <row r="40" spans="1:11" ht="24" customHeight="1">
-      <c r="A40" s="55"/>
+      <c r="A40" s="41"/>
       <c r="B40" s="19" t="str">
         <f>RUBRICA!A5</f>
         <v xml:space="preserve">2. Presenta las evidencias del Proyecto APT, dando cuenta del cumplimiento de los objetivos y de acuerdo a los estándares de la disciplina. </v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D40" s="12" t="str">
         <f t="shared" si="12"/>
@@ -2201,13 +2202,13 @@
       </c>
     </row>
     <row r="41" spans="1:11" ht="24" customHeight="1">
-      <c r="A41" s="55"/>
+      <c r="A41" s="41"/>
       <c r="B41" s="19" t="str">
         <f>RUBRICA!A6</f>
         <v>3. Responde las preguntas realizadas por la comisión, cumpliendo con los estándares de calidad de la disciplina.</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D41" s="12" t="str">
         <f t="shared" si="12"/>
@@ -2243,13 +2244,13 @@
       </c>
     </row>
     <row r="42" spans="1:11" ht="24" customHeight="1">
-      <c r="A42" s="55"/>
+      <c r="A42" s="41"/>
       <c r="B42" s="19" t="str">
         <f>RUBRICA!A7</f>
         <v>4. Expone el Proyecto APT, considerando el formato y el tiempo establecido para la presentación.</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D42" s="12" t="str">
         <f t="shared" si="12"/>
@@ -2285,13 +2286,13 @@
       </c>
     </row>
     <row r="43" spans="1:11" ht="24" customHeight="1">
-      <c r="A43" s="55"/>
+      <c r="A43" s="41"/>
       <c r="B43" s="19" t="str">
         <f>RUBRICA!A8</f>
         <v>5. Expresa sus ideas con fluidez, claridad y precisión, utilizando lenguaje técnico propio de la disciplina.</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D43" s="12" t="str">
         <f t="shared" si="12"/>
@@ -2327,13 +2328,13 @@
       </c>
     </row>
     <row r="44" spans="1:11" ht="24" customHeight="1">
-      <c r="A44" s="55"/>
+      <c r="A44" s="41"/>
       <c r="B44" s="19" t="str">
         <f>RUBRICA!A9</f>
         <v>6. Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estructura y nombres solicitados, guardando todas las evidencias de avances en Git</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D44" s="12" t="str">
         <f>IF($C44=CL,"X","")</f>
@@ -2369,13 +2370,13 @@
       </c>
     </row>
     <row r="45" spans="1:11" ht="24" customHeight="1">
-      <c r="A45" s="55"/>
+      <c r="A45" s="41"/>
       <c r="B45" s="19" t="str">
         <f>RUBRICA!A10</f>
         <v xml:space="preserve">7. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. </v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D45" s="12" t="str">
         <f>IF($C45=CL,"X","")</f>
@@ -2411,9 +2412,9 @@
       </c>
     </row>
     <row r="46" spans="1:11" ht="24" customHeight="1">
-      <c r="A46" s="53"/>
+      <c r="A46" s="40"/>
       <c r="B46" s="18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C46" s="22">
         <f>E46+G46+I46+K46</f>
@@ -2441,9 +2442,9 @@
       </c>
     </row>
     <row r="47" spans="1:11" ht="24" customHeight="1">
-      <c r="A47" s="54"/>
+      <c r="A47" s="42"/>
       <c r="B47" s="21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C47" s="14">
         <f>VLOOKUP(C46,ESCALA_IEP!A28:B228,2,FALSE)</f>
@@ -2453,58 +2454,58 @@
     <row r="48" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="49" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="50" spans="1:11" ht="24" customHeight="1">
-      <c r="A50" s="38" t="s">
-        <v>17</v>
+      <c r="A50" s="39" t="s">
+        <v>14</v>
       </c>
       <c r="B50" s="11" t="str">
         <f>B4</f>
         <v>Axel Cardenas</v>
       </c>
-      <c r="C50" s="39" t="s">
+      <c r="C50" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="45"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="46"/>
+    </row>
+    <row r="51" spans="1:11" ht="24" customHeight="1">
+      <c r="A51" s="40"/>
+      <c r="B51" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="42"/>
+      <c r="D51" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="D50" s="40" t="s">
+      <c r="E51" s="46"/>
+      <c r="F51" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="51"/>
-      <c r="J50" s="51"/>
-      <c r="K50" s="52"/>
-    </row>
-    <row r="51" spans="1:11" ht="24" customHeight="1">
-      <c r="A51" s="53"/>
-      <c r="B51" s="15" t="s">
+      <c r="G51" s="46"/>
+      <c r="H51" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C51" s="54"/>
-      <c r="D51" s="40" t="s">
+      <c r="I51" s="46"/>
+      <c r="J51" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="52"/>
-      <c r="F51" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G51" s="52"/>
-      <c r="H51" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="I51" s="52"/>
-      <c r="J51" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="K51" s="52"/>
+      <c r="K51" s="46"/>
     </row>
     <row r="52" spans="1:11" ht="24" customHeight="1">
-      <c r="A52" s="55"/>
+      <c r="A52" s="41"/>
       <c r="B52" s="19" t="str">
         <f>RUBRICA!A4</f>
         <v xml:space="preserve">1. Presenta el proyecto considerando la relevancia, objetivos, metodología y desarrollo, de acuerdo a los estándares de calidad de la disciplina. </v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D52" s="12" t="str">
         <f t="shared" ref="D52:D56" si="17">IF($C52=CL,"X","")</f>
@@ -2540,13 +2541,13 @@
       </c>
     </row>
     <row r="53" spans="1:11" ht="24" customHeight="1">
-      <c r="A53" s="55"/>
+      <c r="A53" s="41"/>
       <c r="B53" s="19" t="str">
         <f>RUBRICA!A5</f>
         <v xml:space="preserve">2. Presenta las evidencias del Proyecto APT, dando cuenta del cumplimiento de los objetivos y de acuerdo a los estándares de la disciplina. </v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D53" s="12" t="str">
         <f t="shared" si="17"/>
@@ -2582,13 +2583,13 @@
       </c>
     </row>
     <row r="54" spans="1:11" ht="24" customHeight="1">
-      <c r="A54" s="55"/>
+      <c r="A54" s="41"/>
       <c r="B54" s="19" t="str">
         <f>RUBRICA!A6</f>
         <v>3. Responde las preguntas realizadas por la comisión, cumpliendo con los estándares de calidad de la disciplina.</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D54" s="12" t="str">
         <f t="shared" si="17"/>
@@ -2624,13 +2625,13 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="24" customHeight="1">
-      <c r="A55" s="55"/>
+      <c r="A55" s="41"/>
       <c r="B55" s="19" t="str">
         <f>RUBRICA!A7</f>
         <v>4. Expone el Proyecto APT, considerando el formato y el tiempo establecido para la presentación.</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D55" s="12" t="str">
         <f t="shared" si="17"/>
@@ -2666,13 +2667,13 @@
       </c>
     </row>
     <row r="56" spans="1:11" ht="24" customHeight="1">
-      <c r="A56" s="55"/>
+      <c r="A56" s="41"/>
       <c r="B56" s="19" t="str">
         <f>RUBRICA!A8</f>
         <v>5. Expresa sus ideas con fluidez, claridad y precisión, utilizando lenguaje técnico propio de la disciplina.</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D56" s="12" t="str">
         <f t="shared" si="17"/>
@@ -2708,13 +2709,13 @@
       </c>
     </row>
     <row r="57" spans="1:11" ht="24" customHeight="1">
-      <c r="A57" s="55"/>
+      <c r="A57" s="41"/>
       <c r="B57" s="19" t="str">
         <f>RUBRICA!A9</f>
         <v>6. Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estructura y nombres solicitados, guardando todas las evidencias de avances en Git</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D57" s="12" t="str">
         <f>IF($C57=CL,"X","")</f>
@@ -2750,13 +2751,13 @@
       </c>
     </row>
     <row r="58" spans="1:11" ht="24" customHeight="1">
-      <c r="A58" s="55"/>
+      <c r="A58" s="41"/>
       <c r="B58" s="19" t="str">
         <f>RUBRICA!A10</f>
         <v xml:space="preserve">7. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. </v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D58" s="12" t="str">
         <f>IF($C58=CL,"X","")</f>
@@ -2792,9 +2793,9 @@
       </c>
     </row>
     <row r="59" spans="1:11" ht="24" customHeight="1">
-      <c r="A59" s="53"/>
+      <c r="A59" s="40"/>
       <c r="B59" s="18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C59" s="22">
         <f>E59+G59+I59+K59</f>
@@ -2822,9 +2823,9 @@
       </c>
     </row>
     <row r="60" spans="1:11" ht="24" customHeight="1">
-      <c r="A60" s="54"/>
+      <c r="A60" s="42"/>
       <c r="B60" s="21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C60" s="14">
         <f>VLOOKUP(C59,ESCALA_IEP!A41:B241,2,FALSE)</f>
@@ -2834,58 +2835,58 @@
     <row r="61" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="62" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="63" spans="1:11" ht="24" customHeight="1">
-      <c r="A63" s="38" t="s">
-        <v>18</v>
+      <c r="A63" s="39" t="s">
+        <v>15</v>
       </c>
       <c r="B63" s="11" t="str">
         <f>B5</f>
         <v>Diego Castillo</v>
       </c>
-      <c r="C63" s="39" t="s">
+      <c r="C63" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="E63" s="45"/>
+      <c r="F63" s="45"/>
+      <c r="G63" s="45"/>
+      <c r="H63" s="45"/>
+      <c r="I63" s="45"/>
+      <c r="J63" s="45"/>
+      <c r="K63" s="46"/>
+    </row>
+    <row r="64" spans="1:11" ht="24" customHeight="1">
+      <c r="A64" s="40"/>
+      <c r="B64" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="42"/>
+      <c r="D64" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="D63" s="40" t="s">
+      <c r="E64" s="46"/>
+      <c r="F64" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="E63" s="51"/>
-      <c r="F63" s="51"/>
-      <c r="G63" s="51"/>
-      <c r="H63" s="51"/>
-      <c r="I63" s="51"/>
-      <c r="J63" s="51"/>
-      <c r="K63" s="52"/>
-    </row>
-    <row r="64" spans="1:11" ht="24" customHeight="1">
-      <c r="A64" s="53"/>
-      <c r="B64" s="15" t="s">
+      <c r="G64" s="46"/>
+      <c r="H64" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C64" s="54"/>
-      <c r="D64" s="40" t="s">
+      <c r="I64" s="46"/>
+      <c r="J64" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E64" s="52"/>
-      <c r="F64" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G64" s="52"/>
-      <c r="H64" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="I64" s="52"/>
-      <c r="J64" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="K64" s="52"/>
+      <c r="K64" s="46"/>
     </row>
     <row r="65" spans="1:11" ht="24" customHeight="1">
-      <c r="A65" s="55"/>
+      <c r="A65" s="41"/>
       <c r="B65" s="19" t="str">
         <f>RUBRICA!A4</f>
         <v xml:space="preserve">1. Presenta el proyecto considerando la relevancia, objetivos, metodología y desarrollo, de acuerdo a los estándares de calidad de la disciplina. </v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D65" s="12" t="str">
         <f t="shared" ref="D65:D69" si="22">IF($C65=CL,"X","")</f>
@@ -2921,13 +2922,13 @@
       </c>
     </row>
     <row r="66" spans="1:11" ht="24" customHeight="1">
-      <c r="A66" s="55"/>
+      <c r="A66" s="41"/>
       <c r="B66" s="19" t="str">
         <f>RUBRICA!A5</f>
         <v xml:space="preserve">2. Presenta las evidencias del Proyecto APT, dando cuenta del cumplimiento de los objetivos y de acuerdo a los estándares de la disciplina. </v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D66" s="12" t="str">
         <f t="shared" si="22"/>
@@ -2963,13 +2964,13 @@
       </c>
     </row>
     <row r="67" spans="1:11" ht="24" customHeight="1">
-      <c r="A67" s="55"/>
+      <c r="A67" s="41"/>
       <c r="B67" s="19" t="str">
         <f>RUBRICA!A6</f>
         <v>3. Responde las preguntas realizadas por la comisión, cumpliendo con los estándares de calidad de la disciplina.</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D67" s="12" t="str">
         <f t="shared" si="22"/>
@@ -3005,13 +3006,13 @@
       </c>
     </row>
     <row r="68" spans="1:11" ht="24" customHeight="1">
-      <c r="A68" s="55"/>
+      <c r="A68" s="41"/>
       <c r="B68" s="19" t="str">
         <f>RUBRICA!A7</f>
         <v>4. Expone el Proyecto APT, considerando el formato y el tiempo establecido para la presentación.</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D68" s="12" t="str">
         <f t="shared" si="22"/>
@@ -3047,13 +3048,13 @@
       </c>
     </row>
     <row r="69" spans="1:11" ht="24" customHeight="1">
-      <c r="A69" s="55"/>
+      <c r="A69" s="41"/>
       <c r="B69" s="19" t="str">
         <f>RUBRICA!A8</f>
         <v>5. Expresa sus ideas con fluidez, claridad y precisión, utilizando lenguaje técnico propio de la disciplina.</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D69" s="12" t="str">
         <f t="shared" si="22"/>
@@ -3089,13 +3090,13 @@
       </c>
     </row>
     <row r="70" spans="1:11" ht="24" customHeight="1">
-      <c r="A70" s="55"/>
+      <c r="A70" s="41"/>
       <c r="B70" s="19" t="str">
         <f>RUBRICA!A9</f>
         <v>6. Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estructura y nombres solicitados, guardando todas las evidencias de avances en Git</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D70" s="12" t="str">
         <f>IF($C70=CL,"X","")</f>
@@ -3131,13 +3132,13 @@
       </c>
     </row>
     <row r="71" spans="1:11" ht="24" customHeight="1">
-      <c r="A71" s="55"/>
+      <c r="A71" s="41"/>
       <c r="B71" s="19" t="str">
         <f>RUBRICA!A10</f>
         <v xml:space="preserve">7. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. </v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D71" s="12" t="str">
         <f>IF($C71=CL,"X","")</f>
@@ -3173,9 +3174,9 @@
       </c>
     </row>
     <row r="72" spans="1:11" ht="24" customHeight="1">
-      <c r="A72" s="53"/>
+      <c r="A72" s="40"/>
       <c r="B72" s="18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C72" s="22">
         <f>E72+G72+I72+K72</f>
@@ -3203,9 +3204,9 @@
       </c>
     </row>
     <row r="73" spans="1:11" ht="24" customHeight="1">
-      <c r="A73" s="54"/>
+      <c r="A73" s="42"/>
       <c r="B73" s="21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C73" s="14">
         <f>VLOOKUP(C72,ESCALA_IEP!A54:B254,2,FALSE)</f>
@@ -3215,58 +3216,58 @@
     <row r="74" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="75" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="76" spans="1:11" ht="24" customHeight="1">
-      <c r="A76" s="38" t="s">
-        <v>19</v>
+      <c r="A76" s="39" t="s">
+        <v>16</v>
       </c>
       <c r="B76" s="11" t="str">
         <f>B6</f>
         <v>Diego Vargas</v>
       </c>
-      <c r="C76" s="39" t="s">
+      <c r="C76" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="E76" s="45"/>
+      <c r="F76" s="45"/>
+      <c r="G76" s="45"/>
+      <c r="H76" s="45"/>
+      <c r="I76" s="45"/>
+      <c r="J76" s="45"/>
+      <c r="K76" s="46"/>
+    </row>
+    <row r="77" spans="1:11" ht="24" customHeight="1">
+      <c r="A77" s="40"/>
+      <c r="B77" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="42"/>
+      <c r="D77" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="D76" s="40" t="s">
+      <c r="E77" s="46"/>
+      <c r="F77" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="E76" s="51"/>
-      <c r="F76" s="51"/>
-      <c r="G76" s="51"/>
-      <c r="H76" s="51"/>
-      <c r="I76" s="51"/>
-      <c r="J76" s="51"/>
-      <c r="K76" s="52"/>
-    </row>
-    <row r="77" spans="1:11" ht="24" customHeight="1">
-      <c r="A77" s="53"/>
-      <c r="B77" s="15" t="s">
+      <c r="G77" s="46"/>
+      <c r="H77" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C77" s="54"/>
-      <c r="D77" s="40" t="s">
+      <c r="I77" s="46"/>
+      <c r="J77" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E77" s="52"/>
-      <c r="F77" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G77" s="52"/>
-      <c r="H77" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="I77" s="52"/>
-      <c r="J77" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="K77" s="52"/>
+      <c r="K77" s="46"/>
     </row>
     <row r="78" spans="1:11" ht="24" customHeight="1">
-      <c r="A78" s="55"/>
+      <c r="A78" s="41"/>
       <c r="B78" s="19" t="str">
         <f>RUBRICA!A4</f>
         <v xml:space="preserve">1. Presenta el proyecto considerando la relevancia, objetivos, metodología y desarrollo, de acuerdo a los estándares de calidad de la disciplina. </v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D78" s="12" t="str">
         <f t="shared" ref="D78:D82" si="27">IF($C78=CL,"X","")</f>
@@ -3302,13 +3303,13 @@
       </c>
     </row>
     <row r="79" spans="1:11" ht="24" customHeight="1">
-      <c r="A79" s="55"/>
+      <c r="A79" s="41"/>
       <c r="B79" s="19" t="str">
         <f>RUBRICA!A5</f>
         <v xml:space="preserve">2. Presenta las evidencias del Proyecto APT, dando cuenta del cumplimiento de los objetivos y de acuerdo a los estándares de la disciplina. </v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D79" s="12" t="str">
         <f t="shared" si="27"/>
@@ -3344,13 +3345,13 @@
       </c>
     </row>
     <row r="80" spans="1:11" ht="24" customHeight="1">
-      <c r="A80" s="55"/>
+      <c r="A80" s="41"/>
       <c r="B80" s="19" t="str">
         <f>RUBRICA!A6</f>
         <v>3. Responde las preguntas realizadas por la comisión, cumpliendo con los estándares de calidad de la disciplina.</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D80" s="12" t="str">
         <f t="shared" si="27"/>
@@ -3386,13 +3387,13 @@
       </c>
     </row>
     <row r="81" spans="1:11" ht="24" customHeight="1">
-      <c r="A81" s="55"/>
+      <c r="A81" s="41"/>
       <c r="B81" s="19" t="str">
         <f>RUBRICA!A7</f>
         <v>4. Expone el Proyecto APT, considerando el formato y el tiempo establecido para la presentación.</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D81" s="12" t="str">
         <f t="shared" si="27"/>
@@ -3428,13 +3429,13 @@
       </c>
     </row>
     <row r="82" spans="1:11" ht="24" customHeight="1">
-      <c r="A82" s="55"/>
+      <c r="A82" s="41"/>
       <c r="B82" s="19" t="str">
         <f>RUBRICA!A8</f>
         <v>5. Expresa sus ideas con fluidez, claridad y precisión, utilizando lenguaje técnico propio de la disciplina.</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D82" s="12" t="str">
         <f t="shared" si="27"/>
@@ -3470,13 +3471,13 @@
       </c>
     </row>
     <row r="83" spans="1:11" ht="24" customHeight="1">
-      <c r="A83" s="55"/>
+      <c r="A83" s="41"/>
       <c r="B83" s="19" t="str">
         <f>RUBRICA!A9</f>
         <v>6. Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estructura y nombres solicitados, guardando todas las evidencias de avances en Git</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D83" s="12" t="str">
         <f>IF($C83=CL,"X","")</f>
@@ -3512,13 +3513,13 @@
       </c>
     </row>
     <row r="84" spans="1:11" ht="24" customHeight="1">
-      <c r="A84" s="55"/>
+      <c r="A84" s="41"/>
       <c r="B84" s="19" t="str">
         <f>RUBRICA!A10</f>
         <v xml:space="preserve">7. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. </v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D84" s="12" t="str">
         <f>IF($C84=CL,"X","")</f>
@@ -3554,9 +3555,9 @@
       </c>
     </row>
     <row r="85" spans="1:11" ht="24" customHeight="1">
-      <c r="A85" s="53"/>
+      <c r="A85" s="40"/>
       <c r="B85" s="18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C85" s="22">
         <f>E85+G85+I85+K85</f>
@@ -3584,9 +3585,9 @@
       </c>
     </row>
     <row r="86" spans="1:11" ht="24" customHeight="1">
-      <c r="A86" s="54"/>
+      <c r="A86" s="42"/>
       <c r="B86" s="21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C86" s="14">
         <f>VLOOKUP(C85,ESCALA_IEP!A67:B267,2,FALSE)</f>
@@ -4383,7 +4384,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90033408-0576-4312-BE07-614F98081636}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.5703125" customWidth="1"/>
     <col min="2" max="2" width="31.28515625" customWidth="1"/>
@@ -4393,63 +4394,63 @@
     <col min="6" max="6" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A1" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="49" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="50"/>
+      <c r="B2" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="C2" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="43" t="s">
+      <c r="D2" s="25" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="44"/>
-      <c r="B2" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>25</v>
-      </c>
       <c r="E2" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="44"/>
+        <v>11</v>
+      </c>
+      <c r="F2" s="50"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="44"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
       <c r="D3" s="27">
         <v>0.3</v>
       </c>
       <c r="E3" s="27">
         <v>0</v>
       </c>
-      <c r="F3" s="44"/>
-    </row>
-    <row r="4" spans="1:6" ht="110.45">
+      <c r="F3" s="50"/>
+    </row>
+    <row r="4" spans="1:6" ht="102">
       <c r="A4" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="E4" s="23" t="s">
         <v>27</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>30</v>
       </c>
       <c r="F4" s="28">
         <v>15</v>
@@ -4457,19 +4458,19 @@
     </row>
     <row r="5" spans="1:6" ht="136.9" customHeight="1">
       <c r="A5" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="E5" s="23" t="s">
         <v>32</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>35</v>
       </c>
       <c r="F5" s="28">
         <v>25</v>
@@ -4477,79 +4478,79 @@
     </row>
     <row r="6" spans="1:6" ht="87" customHeight="1">
       <c r="A6" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="E6" s="23" t="s">
         <v>37</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>40</v>
       </c>
       <c r="F6" s="28">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="96.6">
+    <row r="7" spans="1:6" ht="89.25">
       <c r="A7" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="E7" s="23" t="s">
         <v>42</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>45</v>
       </c>
       <c r="F7" s="28">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="96.6">
+    <row r="8" spans="1:6" ht="89.25">
       <c r="A8" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="E8" s="23" t="s">
         <v>47</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>50</v>
       </c>
       <c r="F8" s="28">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="96.6">
+    <row r="9" spans="1:6" ht="89.25">
       <c r="A9" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="E9" s="23" t="s">
         <v>52</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>55</v>
       </c>
       <c r="F9" s="24">
         <v>20</v>
@@ -4557,19 +4558,19 @@
     </row>
     <row r="10" spans="1:6" ht="126" customHeight="1">
       <c r="A10" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="E10" s="23" t="s">
         <v>57</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>60</v>
       </c>
       <c r="F10" s="24">
         <v>10</v>
@@ -4590,20 +4591,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="14.45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4611,7 +4612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.45">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>0.5</v>
       </c>
@@ -4619,7 +4620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.45">
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4627,7 +4628,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.45">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>1.5</v>
       </c>
@@ -4635,7 +4636,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.45">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -4643,7 +4644,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.45">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>2.5</v>
       </c>
@@ -4651,7 +4652,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.45">
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>3</v>
       </c>
@@ -4659,7 +4660,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.45">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>3.5</v>
       </c>
@@ -4667,7 +4668,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.45">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>4</v>
       </c>
@@ -4675,7 +4676,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.45">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>4.5</v>
       </c>
@@ -4683,7 +4684,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="14.45">
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>5</v>
       </c>
@@ -4691,7 +4692,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.45">
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>5.5</v>
       </c>
@@ -4699,7 +4700,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.45">
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>6</v>
       </c>
@@ -4707,7 +4708,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14.45">
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>6.5</v>
       </c>
@@ -4715,7 +4716,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.45">
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>7</v>
       </c>
@@ -4723,7 +4724,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="14.45">
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>7.5</v>
       </c>
@@ -4731,7 +4732,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.45">
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>8</v>
       </c>
@@ -4739,7 +4740,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.45">
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>8.5</v>
       </c>
@@ -4747,7 +4748,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.45">
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>9</v>
       </c>
@@ -7018,20 +7019,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="14.45">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -7039,7 +7040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.45">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7047,7 +7048,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.45">
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -7055,7 +7056,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.45">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -7063,7 +7064,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.45">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -7071,7 +7072,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.45">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -7079,7 +7080,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.45">
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -7087,7 +7088,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.45">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -7095,7 +7096,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.45">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -7103,7 +7104,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.45">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -7111,7 +7112,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="14.45">
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -7119,7 +7120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.45">
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>11</v>
       </c>
@@ -7127,7 +7128,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.45">
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>12</v>
       </c>
@@ -7135,7 +7136,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14.45">
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>13</v>
       </c>
@@ -7143,7 +7144,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.45">
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>14</v>
       </c>
@@ -7151,7 +7152,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="14.45">
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>15</v>
       </c>
@@ -7159,7 +7160,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.45">
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>16</v>
       </c>
@@ -7167,7 +7168,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.45">
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>17</v>
       </c>
@@ -7175,7 +7176,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.45">
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>18</v>
       </c>
@@ -8410,20 +8411,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="14.45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -8431,7 +8432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.45">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>0.5</v>
       </c>
@@ -8439,7 +8440,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.45">
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -8447,7 +8448,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.45">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>1.5</v>
       </c>
@@ -8455,7 +8456,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.45">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -8463,7 +8464,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.45">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>2.5</v>
       </c>
@@ -8471,7 +8472,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.45">
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>3</v>
       </c>
@@ -8479,7 +8480,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.45">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>3.5</v>
       </c>
@@ -8487,7 +8488,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.45">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>4</v>
       </c>
@@ -8495,7 +8496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.45">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>4.5</v>
       </c>
@@ -8503,7 +8504,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="14.45">
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>5</v>
       </c>
@@ -8511,7 +8512,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.45">
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>5.5</v>
       </c>
@@ -8519,7 +8520,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.45">
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>6</v>
       </c>
@@ -8527,7 +8528,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14.45">
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>6.5</v>
       </c>
@@ -8535,7 +8536,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.45">
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>7</v>
       </c>
@@ -8543,7 +8544,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="14.45">
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>7.5</v>
       </c>
@@ -8551,7 +8552,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.45">
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>8</v>
       </c>
@@ -8559,7 +8560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.45">
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>8.5</v>
       </c>
@@ -8567,7 +8568,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.45">
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>9</v>
       </c>
@@ -9722,40 +9723,40 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="25" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.45">
-      <c r="A1" s="50" t="s">
-        <v>63</v>
+    <row r="1" spans="1:5">
+      <c r="A1" s="56" t="s">
+        <v>60</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" ht="43.9" thickBot="1">
-      <c r="A2" s="56"/>
+    <row r="2" spans="1:5" ht="45.75" thickBot="1">
+      <c r="A2" s="57"/>
       <c r="B2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E2" s="57" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="29.45" thickBot="1">
+    </row>
+    <row r="3" spans="1:5" ht="30.75" thickBot="1">
       <c r="A3" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B3" s="10">
         <v>4</v>
@@ -9770,14 +9771,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" thickBot="1">
+    <row r="4" spans="1:5" ht="15.75" thickBot="1">
       <c r="A4" s="9"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:5" thickBot="1">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1">
       <c r="A5" s="9"/>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
